--- a/Top20Instances_12-25-2025.xlsx
+++ b/Top20Instances_12-25-2025.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VTV</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -525,7 +525,7 @@
         <v>2.690780767534173</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4664420834413097</v>
+        <v>0.2305354710258722</v>
       </c>
       <c r="K2" t="n">
         <v>0.5</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1245,41 +1245,41 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AG</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F19" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="G19" t="n">
         <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>1.000000000000004</v>
+        <v>12.91999999999996</v>
       </c>
       <c r="I19" t="n">
-        <v>1.98550291145978</v>
+        <v>1.024485196188918</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2298216785711626</v>
+        <v>0.4796649101472594</v>
       </c>
       <c r="K19" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2.481878639324725</v>
+        <v>2.561212990472295</v>
       </c>
     </row>
     <row r="20">
@@ -1289,41 +1289,41 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AKR</t>
+          <t>AG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>0.045</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7199999999999989</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="I20" t="n">
-        <v>1.37684854665987</v>
+        <v>1.98550291145978</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06869704602703308</v>
+        <v>0.2298216785711626</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="L20" t="n">
-        <v>2.478327383987766</v>
+        <v>2.481878639324725</v>
       </c>
     </row>
     <row r="21">
@@ -1333,11 +1333,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ABCB</t>
+          <t>AKR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1352,22 +1352,22 @@
         <v>0.01</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>5.129999999999995</v>
+        <v>0.7199999999999989</v>
       </c>
       <c r="I21" t="n">
-        <v>1.575741525423724</v>
+        <v>1.37684854665987</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2814998311001071</v>
+        <v>0.06869704602703308</v>
       </c>
       <c r="K21" t="n">
         <v>0.3</v>
       </c>
       <c r="L21" t="n">
-        <v>2.363612288135586</v>
+        <v>2.478327383987766</v>
       </c>
     </row>
   </sheetData>

--- a/Top20Instances_12-25-2025.xlsx
+++ b/Top20Instances_12-25-2025.xlsx
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AAUC</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -510,28 +510,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.150000000000002</v>
+        <v>40.75000000000003</v>
       </c>
       <c r="I2" t="n">
-        <v>2.690780767534173</v>
+        <v>3.496730259957848</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2305354710258722</v>
+        <v>-0.1586042823156331</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L2" t="n">
-        <v>8.072342302602518</v>
+        <v>8.74182564989462</v>
       </c>
     </row>
     <row r="3">
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AAUC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,28 +554,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.710000000000001</v>
+        <v>3.150000000000002</v>
       </c>
       <c r="I3" t="n">
-        <v>4.865649963689189</v>
+        <v>2.690780767534173</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6692222727568087</v>
+        <v>0.4664420834413097</v>
       </c>
       <c r="K3" t="n">
         <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>7.298474945533783</v>
+        <v>8.072342302602518</v>
       </c>
     </row>
     <row r="4">
@@ -585,41 +585,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ACHR</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.035</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6300000000000017</v>
+        <v>1.710000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.408464418755885</v>
+        <v>4.865649963689189</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2073250504833424</v>
+        <v>0.6692222727568087</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>6.021161046889713</v>
+        <v>7.298474945533783</v>
       </c>
     </row>
     <row r="5">
@@ -629,41 +629,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>ACHR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.070000000000002</v>
+        <v>0.6300000000000017</v>
       </c>
       <c r="I5" t="n">
-        <v>3.007758886765577</v>
+        <v>2.408464418755885</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08879974397934531</v>
+        <v>0.2073250504833424</v>
       </c>
       <c r="K5" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>6.015517773531154</v>
+        <v>6.021161046889713</v>
       </c>
     </row>
     <row r="6">
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AEO</t>
+          <t>ACVA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -692,22 +692,22 @@
         <v>0.03</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.649999999999999</v>
+        <v>1.070000000000002</v>
       </c>
       <c r="I6" t="n">
-        <v>4.474486137271294</v>
+        <v>3.007758886765577</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002485513236755166</v>
+        <v>0.08879974397934531</v>
       </c>
       <c r="K6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>5.593107671589117</v>
+        <v>6.015517773531154</v>
       </c>
     </row>
     <row r="7">
@@ -717,41 +717,41 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALLY</t>
+          <t>AEO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01</v>
+        <v>0.035</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.560000000000002</v>
+        <v>4.649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.492143933859225</v>
+        <v>4.474486137271294</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9948914752300642</v>
+        <v>0.01704922446130186</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L7" t="n">
-        <v>4.476431801577675</v>
+        <v>5.593107671589117</v>
       </c>
     </row>
     <row r="8">
@@ -761,41 +761,41 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>AMTD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F8" t="n">
-        <v>0.015</v>
+        <v>0.045</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>7.540000000000006</v>
+        <v>0.1085999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.274369570205292</v>
+        <v>3.441212617779588</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2769458300913796</v>
+        <v>-2.223625140291818</v>
       </c>
       <c r="K8" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>4.460293495718522</v>
+        <v>5.161818926669382</v>
       </c>
     </row>
     <row r="9">
@@ -805,41 +805,41 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>ALLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.969999999999992</v>
+        <v>4.560000000000002</v>
       </c>
       <c r="I9" t="n">
-        <v>2.189433603046154</v>
+        <v>1.492143933859225</v>
       </c>
       <c r="J9" t="n">
-        <v>1.324159418408399</v>
+        <v>0.9948914752300642</v>
       </c>
       <c r="K9" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>4.378867206092308</v>
+        <v>4.476431801577675</v>
       </c>
     </row>
     <row r="10">
@@ -853,37 +853,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>ALC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>9.210000000000008</v>
+        <v>7.540000000000006</v>
       </c>
       <c r="I10" t="n">
-        <v>2.183494892725291</v>
+        <v>1.274369570205292</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3316556314104047</v>
+        <v>-0.2769458300913796</v>
       </c>
       <c r="K10" t="n">
         <v>0.5</v>
       </c>
       <c r="L10" t="n">
-        <v>4.366989785450582</v>
+        <v>4.460293495718522</v>
       </c>
     </row>
     <row r="11">
@@ -893,41 +893,41 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>9.870000000000033</v>
+        <v>3.969999999999992</v>
       </c>
       <c r="I11" t="n">
-        <v>1.639849385018832</v>
+        <v>2.189433603046154</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05687865706781592</v>
+        <v>1.324159418408399</v>
       </c>
       <c r="K11" t="n">
         <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>4.09962346254708</v>
+        <v>4.378867206092308</v>
       </c>
     </row>
     <row r="12">
@@ -937,41 +937,41 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AHH</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F12" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3200000000000003</v>
+        <v>9.210000000000008</v>
       </c>
       <c r="I12" t="n">
-        <v>2.476780185758509</v>
+        <v>2.183494892725291</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3131047840503998</v>
+        <v>0.3316556314104047</v>
       </c>
       <c r="K12" t="n">
         <v>0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>3.715170278637763</v>
+        <v>4.366989785450582</v>
       </c>
     </row>
     <row r="13">
@@ -981,41 +981,41 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.005</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.015</v>
-      </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>3.839999999999989</v>
+        <v>9.870000000000033</v>
       </c>
       <c r="I13" t="n">
-        <v>2.45840576111247</v>
+        <v>1.639849385018832</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2681348539558925</v>
+        <v>0.05687865706781592</v>
       </c>
       <c r="K13" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" t="n">
-        <v>3.687608641668705</v>
+        <v>4.09962346254708</v>
       </c>
     </row>
     <row r="14">
@@ -1025,41 +1025,41 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>AHH</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>0.005</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8799999999999972</v>
+        <v>0.3200000000000003</v>
       </c>
       <c r="I14" t="n">
-        <v>1.449275362318825</v>
+        <v>2.476780185758509</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2323480056796168</v>
+        <v>0.3131047840503998</v>
       </c>
       <c r="K14" t="n">
         <v>0.5</v>
       </c>
       <c r="L14" t="n">
-        <v>3.623188405797062</v>
+        <v>3.715170278637763</v>
       </c>
     </row>
     <row r="15">
@@ -1069,41 +1069,41 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AGRO</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F15" t="n">
-        <v>0.045</v>
+        <v>0.015</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9500000000000002</v>
+        <v>3.839999999999989</v>
       </c>
       <c r="I15" t="n">
-        <v>3.561906884638799</v>
+        <v>2.45840576111247</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08770821569733522</v>
+        <v>0.2681348539558925</v>
       </c>
       <c r="K15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L15" t="n">
-        <v>3.561906884638799</v>
+        <v>3.687608641668705</v>
       </c>
     </row>
     <row r="16">
@@ -1113,41 +1113,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACCO</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2399999999999998</v>
+        <v>0.8799999999999972</v>
       </c>
       <c r="I16" t="n">
-        <v>1.162790697674421</v>
+        <v>1.449275362318825</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.08113138511954832</v>
+        <v>0.2323480056796168</v>
       </c>
       <c r="K16" t="n">
         <v>0.5</v>
       </c>
       <c r="L16" t="n">
-        <v>3.488372093023263</v>
+        <v>3.623188405797062</v>
       </c>
     </row>
     <row r="17">
@@ -1157,41 +1157,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>AGRO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>VTV</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01</v>
+        <v>0.045</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7100000000000009</v>
+        <v>0.9500000000000002</v>
       </c>
       <c r="I17" t="n">
-        <v>1.501229186776065</v>
+        <v>3.561906884638799</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2655483797179892</v>
+        <v>0.08770821569733522</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L17" t="n">
-        <v>3.00245837355213</v>
+        <v>3.561906884638799</v>
       </c>
     </row>
     <row r="18">
@@ -1201,41 +1201,41 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AEG</t>
+          <t>ACCO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2700000000000005</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="I18" t="n">
-        <v>1.778846478806595</v>
+        <v>1.162790697674421</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1502937158785356</v>
+        <v>0.2385067404078844</v>
       </c>
       <c r="K18" t="n">
         <v>0.5</v>
       </c>
       <c r="L18" t="n">
-        <v>2.668269718209892</v>
+        <v>3.488372093023263</v>
       </c>
     </row>
     <row r="19">
@@ -1249,37 +1249,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>ACEL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.01</v>
       </c>
-      <c r="F19" t="n">
-        <v>0.025</v>
-      </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>12.91999999999996</v>
+        <v>0.7100000000000009</v>
       </c>
       <c r="I19" t="n">
-        <v>1.024485196188918</v>
+        <v>1.501229186776065</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4796649101472594</v>
+        <v>-0.2655483797179892</v>
       </c>
       <c r="K19" t="n">
         <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2.561212990472295</v>
+        <v>3.00245837355213</v>
       </c>
     </row>
     <row r="20">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AG</t>
+          <t>AMRZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1302,28 +1302,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>1.000000000000004</v>
+        <v>2.479999999999997</v>
       </c>
       <c r="I20" t="n">
-        <v>1.98550291145978</v>
+        <v>1.849084796413902</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2298216785711626</v>
+        <v>0.4952793685188084</v>
       </c>
       <c r="K20" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>2.481878639324725</v>
+        <v>2.773627194620853</v>
       </c>
     </row>
     <row r="21">
@@ -1333,11 +1333,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AKR</t>
+          <t>AEG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1349,25 +1349,25 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7199999999999989</v>
+        <v>0.2700000000000005</v>
       </c>
       <c r="I21" t="n">
-        <v>1.37684854665987</v>
+        <v>1.778846478806595</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06869704602703308</v>
+        <v>0.1502937158785356</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="n">
-        <v>2.478327383987766</v>
+        <v>2.668269718209892</v>
       </c>
     </row>
   </sheetData>

--- a/Top20Instances_12-25-2025.xlsx
+++ b/Top20Instances_12-25-2025.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>ANRO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>40.75000000000003</v>
+        <v>1.619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.496730259957848</v>
+        <v>6.191479952830193</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1586042823156331</v>
+        <v>0.497955154403884</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>8.74182564989462</v>
+        <v>9.287219929245289</v>
       </c>
     </row>
     <row r="3">
@@ -541,41 +541,41 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AAUC</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F3" t="n">
         <v>0.035</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.150000000000002</v>
+        <v>40.75000000000003</v>
       </c>
       <c r="I3" t="n">
-        <v>2.690780767534173</v>
+        <v>3.496730259957848</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4664420834413097</v>
+        <v>-0.3266843460548174</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L3" t="n">
-        <v>8.072342302602518</v>
+        <v>8.74182564989462</v>
       </c>
     </row>
     <row r="4">
@@ -585,41 +585,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AMTD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="F4" t="n">
-        <v>0.025</v>
+        <v>0.04</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.710000000000001</v>
+        <v>0.1085999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4.865649963689189</v>
+        <v>3.441212617779588</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6692222727568087</v>
+        <v>-1.091637755712416</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>7.298474945533783</v>
+        <v>5.161818926669382</v>
       </c>
     </row>
     <row r="5">
@@ -633,37 +633,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACHR</t>
+          <t>AMRZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.035</v>
+        <v>0.015</v>
       </c>
       <c r="F5" t="n">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6300000000000017</v>
+        <v>2.479999999999997</v>
       </c>
       <c r="I5" t="n">
-        <v>2.408464418755885</v>
+        <v>1.849084796413902</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2073250504833424</v>
+        <v>0.4952793685188084</v>
       </c>
       <c r="K5" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>6.021161046889713</v>
+        <v>2.773627194620853</v>
       </c>
     </row>
     <row r="6">
@@ -673,41 +673,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>ANVS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.070000000000002</v>
+        <v>0.2700000000000005</v>
       </c>
       <c r="I6" t="n">
-        <v>3.007758886765577</v>
+        <v>5.442176870748305</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08879974397934531</v>
+        <v>0.3872752420470249</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="L6" t="n">
-        <v>6.015517773531154</v>
+        <v>2.721088435374151</v>
       </c>
     </row>
     <row r="7">
@@ -717,41 +717,41 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AEO</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.649999999999999</v>
+        <v>12.91999999999996</v>
       </c>
       <c r="I7" t="n">
-        <v>4.474486137271294</v>
+        <v>1.024485196188918</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01704922446130186</v>
+        <v>0.4796649101472594</v>
       </c>
       <c r="K7" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>5.593107671589117</v>
+        <v>2.561212990472295</v>
       </c>
     </row>
     <row r="8">
@@ -761,41 +761,41 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMTD</t>
+          <t>AMTB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
-        <v>0.045</v>
+        <v>0.015</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1085999999999999</v>
+        <v>0.6099999999999994</v>
       </c>
       <c r="I8" t="n">
-        <v>3.441212617779588</v>
+        <v>1.608080424194935</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.223625140291818</v>
+        <v>0.09523330198610291</v>
       </c>
       <c r="K8" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>5.161818926669382</v>
+        <v>2.412120636292403</v>
       </c>
     </row>
     <row r="9">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ALLY</t>
+          <t>AOD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -824,22 +824,22 @@
         <v>0.01</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>4.560000000000002</v>
+        <v>0.4100000000000019</v>
       </c>
       <c r="I9" t="n">
-        <v>1.492143933859225</v>
+        <v>0.8319840241796217</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9948914752300642</v>
+        <v>0.4148789037526579</v>
       </c>
       <c r="K9" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>4.476431801577675</v>
+        <v>2.079960060449054</v>
       </c>
     </row>
     <row r="10">
@@ -849,41 +849,41 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>AMPY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F10" t="n">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>7.540000000000006</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>1.274369570205292</v>
+        <v>1.902306318012015</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2769458300913796</v>
+        <v>0.7111381309541365</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L10" t="n">
-        <v>4.460293495718522</v>
+        <v>1.902306318012015</v>
       </c>
     </row>
     <row r="11">
@@ -893,41 +893,41 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>AN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.969999999999992</v>
+        <v>14.17999999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>2.189433603046154</v>
+        <v>1.821860784013596</v>
       </c>
       <c r="J11" t="n">
-        <v>1.324159418408399</v>
+        <v>-0.09645220272003208</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L11" t="n">
-        <v>4.378867206092308</v>
+        <v>1.821860784013596</v>
       </c>
     </row>
     <row r="12">
@@ -937,41 +937,41 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>9.210000000000008</v>
+        <v>0.2900000000000009</v>
       </c>
       <c r="I12" t="n">
-        <v>2.183494892725291</v>
+        <v>0.7142857142857117</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3316556314104047</v>
+        <v>0.2323480056796168</v>
       </c>
       <c r="K12" t="n">
         <v>0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>4.366989785450582</v>
+        <v>1.785714285714279</v>
       </c>
     </row>
     <row r="13">
@@ -981,41 +981,41 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>AMBP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.870000000000033</v>
+        <v>0.2799999999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>1.639849385018832</v>
+        <v>0.7898237445959411</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05687865706781592</v>
+        <v>0.373899882051576</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L13" t="n">
-        <v>4.09962346254708</v>
+        <v>1.777103425340867</v>
       </c>
     </row>
     <row r="14">
@@ -1025,41 +1025,41 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AHH</t>
+          <t>AMX</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005</v>
+        <v>0.045</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3200000000000003</v>
+        <v>0.75</v>
       </c>
       <c r="I14" t="n">
-        <v>2.476780185758509</v>
+        <v>0.8644994048821242</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3131047840503998</v>
+        <v>0.2839605887273278</v>
       </c>
       <c r="K14" t="n">
         <v>0.5</v>
       </c>
       <c r="L14" t="n">
-        <v>3.715170278637763</v>
+        <v>1.728998809764248</v>
       </c>
     </row>
     <row r="15">
@@ -1069,20 +1069,20 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0.015</v>
@@ -1091,19 +1091,19 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>3.839999999999989</v>
+        <v>1.929999999999993</v>
       </c>
       <c r="I15" t="n">
-        <v>2.45840576111247</v>
+        <v>0.9383691042803455</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2681348539558925</v>
+        <v>-0.5122742960086302</v>
       </c>
       <c r="K15" t="n">
         <v>0.5</v>
       </c>
       <c r="L15" t="n">
-        <v>3.687608641668705</v>
+        <v>1.407553656420518</v>
       </c>
     </row>
     <row r="16">
@@ -1113,41 +1113,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="F16" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8799999999999972</v>
+        <v>18.16999999999996</v>
       </c>
       <c r="I16" t="n">
-        <v>1.449275362318825</v>
+        <v>0.5005843826493495</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2323480056796168</v>
+        <v>0.5591436431048979</v>
       </c>
       <c r="K16" t="n">
         <v>0.5</v>
       </c>
       <c r="L16" t="n">
-        <v>3.623188405797062</v>
+        <v>1.251460956623374</v>
       </c>
     </row>
     <row r="17">
@@ -1157,41 +1157,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AGRO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9500000000000002</v>
+        <v>3.989999999999981</v>
       </c>
       <c r="I17" t="n">
-        <v>3.561906884638799</v>
+        <v>0.4536075120139982</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08770821569733522</v>
+        <v>0.6234095735542566</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L17" t="n">
-        <v>3.561906884638799</v>
+        <v>1.058417528032663</v>
       </c>
     </row>
     <row r="18">
@@ -1201,11 +1201,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ACCO</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.005</v>
+        <v>0.03</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2999999999999994</v>
+        <v>0.4899999999999984</v>
       </c>
       <c r="I18" t="n">
-        <v>1.162790697674421</v>
+        <v>0.6853226727584039</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2385067404078844</v>
+        <v>0.2681348539558925</v>
       </c>
       <c r="K18" t="n">
         <v>0.5</v>
       </c>
       <c r="L18" t="n">
-        <v>3.488372093023263</v>
+        <v>1.027984009137606</v>
       </c>
     </row>
     <row r="19">
@@ -1245,41 +1245,41 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ACEL</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7100000000000009</v>
+        <v>0.2800000000000002</v>
       </c>
       <c r="I19" t="n">
-        <v>1.501229186776065</v>
+        <v>1.716738197424905</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2655483797179892</v>
+        <v>0.06869704602703308</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="L19" t="n">
-        <v>3.00245837355213</v>
+        <v>0.9809932556713739</v>
       </c>
     </row>
     <row r="20">
@@ -1289,41 +1289,41 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMRZ</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.479999999999997</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.849084796413902</v>
+        <v>1.878522229179702</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4952793685188084</v>
+        <v>0.1394286392358168</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="L20" t="n">
-        <v>2.773627194620853</v>
+        <v>0.9392611145898505</v>
       </c>
     </row>
     <row r="21">
@@ -1333,41 +1333,41 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AEG</t>
+          <t>AMG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2700000000000005</v>
+        <v>1.090000000000032</v>
       </c>
       <c r="I21" t="n">
-        <v>1.778846478806595</v>
+        <v>0.4333349843953282</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1502937158785356</v>
+        <v>-0.1048429141118301</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L21" t="n">
-        <v>2.668269718209892</v>
+        <v>0.4333349843953282</v>
       </c>
     </row>
   </sheetData>

--- a/Top20Instances_12-25-2025.xlsx
+++ b/Top20Instances_12-25-2025.xlsx
@@ -497,41 +497,41 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ANRO</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0.045</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>1.619999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="I2" t="n">
-        <v>6.191479952830193</v>
+        <v>5.985037406483795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.497955154403884</v>
+        <v>-0.01830161054172663</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L2" t="n">
-        <v>9.287219929245289</v>
+        <v>14.96259351620949</v>
       </c>
     </row>
     <row r="3">
@@ -545,37 +545,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>ANRO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.035</v>
+        <v>0.045</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>40.75000000000003</v>
+        <v>1.619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.496730259957848</v>
+        <v>6.191479952830193</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3266843460548174</v>
+        <v>0.59560983074749</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>8.74182564989462</v>
+        <v>9.287219929245289</v>
       </c>
     </row>
     <row r="4">
@@ -585,41 +585,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AMTD</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>VTV</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1085999999999999</v>
+        <v>40.75000000000003</v>
       </c>
       <c r="I4" t="n">
-        <v>3.441212617779588</v>
+        <v>3.496730259957848</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.091637755712416</v>
+        <v>-0.1586042823156331</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L4" t="n">
-        <v>5.161818926669382</v>
+        <v>8.74182564989462</v>
       </c>
     </row>
     <row r="5">
@@ -629,41 +629,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AMRZ</t>
+          <t>AMTD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.479999999999997</v>
+        <v>0.1085999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.849084796413902</v>
+        <v>3.441212617779588</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4952793685188084</v>
+        <v>-2.223625140291818</v>
       </c>
       <c r="K5" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>2.773627194620853</v>
+        <v>5.161818926669382</v>
       </c>
     </row>
     <row r="6">
@@ -673,41 +673,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANVS</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2700000000000005</v>
+        <v>2.939999999999998</v>
       </c>
       <c r="I6" t="n">
-        <v>5.442176870748305</v>
+        <v>2.043681747269899</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3872752420470249</v>
+        <v>0.2555271636484724</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>2.721088435374151</v>
+        <v>3.065522620904849</v>
       </c>
     </row>
     <row r="7">
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AOMR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -739,19 +739,19 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>12.91999999999996</v>
+        <v>0.4600000000000009</v>
       </c>
       <c r="I7" t="n">
-        <v>1.024485196188918</v>
+        <v>1.198699821225424</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4796649101472594</v>
+        <v>1.013212284495868</v>
       </c>
       <c r="K7" t="n">
         <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>2.561212990472295</v>
+        <v>2.99674955306356</v>
       </c>
     </row>
     <row r="8">
@@ -761,41 +761,41 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMTB</t>
+          <t>AMRZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6099999999999994</v>
+        <v>2.479999999999997</v>
       </c>
       <c r="I8" t="n">
-        <v>1.608080424194935</v>
+        <v>1.849084796413902</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09523330198610291</v>
+        <v>0.4952793685188084</v>
       </c>
       <c r="K8" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>2.412120636292403</v>
+        <v>2.773627194620853</v>
       </c>
     </row>
     <row r="9">
@@ -805,41 +805,41 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AOD</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4100000000000019</v>
+        <v>16.86999999999995</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8319840241796217</v>
+        <v>1.816071946620257</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4148789037526579</v>
+        <v>1.173423335033941</v>
       </c>
       <c r="K9" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>2.079960060449054</v>
+        <v>2.724107919930386</v>
       </c>
     </row>
     <row r="10">
@@ -849,41 +849,41 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AMPY</t>
+          <t>ANVS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="F10" t="n">
         <v>0.04</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.2700000000000005</v>
       </c>
       <c r="I10" t="n">
-        <v>1.902306318012015</v>
+        <v>5.442176870748305</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7111381309541365</v>
+        <v>0.69020744356314</v>
       </c>
       <c r="K10" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="L10" t="n">
-        <v>1.902306318012015</v>
+        <v>2.721088435374151</v>
       </c>
     </row>
     <row r="11">
@@ -893,41 +893,41 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>14.17999999999998</v>
+        <v>12.91999999999996</v>
       </c>
       <c r="I11" t="n">
-        <v>1.821860784013596</v>
+        <v>1.024485196188918</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.09645220272003208</v>
+        <v>0.4796649101472594</v>
       </c>
       <c r="K11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.821860784013596</v>
+        <v>2.561212990472295</v>
       </c>
     </row>
     <row r="12">
@@ -937,41 +937,41 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>AMTB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2900000000000009</v>
+        <v>0.6099999999999994</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7142857142857117</v>
+        <v>1.608080424194935</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2323480056796168</v>
+        <v>0.09523330198610291</v>
       </c>
       <c r="K12" t="n">
         <v>0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.785714285714279</v>
+        <v>2.412120636292403</v>
       </c>
     </row>
     <row r="13">
@@ -981,41 +981,41 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AMBP</t>
+          <t>AOD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2799999999999998</v>
+        <v>0.4100000000000019</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7898237445959411</v>
+        <v>0.8319840241796217</v>
       </c>
       <c r="J13" t="n">
-        <v>0.373899882051576</v>
+        <v>0.4148789037526579</v>
       </c>
       <c r="K13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.777103425340867</v>
+        <v>2.079960060449054</v>
       </c>
     </row>
     <row r="14">
@@ -1029,37 +1029,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AMX</t>
+          <t>AMPY</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.75</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8644994048821242</v>
+        <v>1.902306318012015</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2839605887273278</v>
+        <v>0.7111381309541365</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.728998809764248</v>
+        <v>1.902306318012015</v>
       </c>
     </row>
     <row r="15">
@@ -1069,41 +1069,41 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>AN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F15" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.929999999999993</v>
+        <v>14.17999999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9383691042803455</v>
+        <v>1.821860784013596</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5122742960086302</v>
+        <v>-0.09645220272003208</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.407553656420518</v>
+        <v>1.821860784013596</v>
       </c>
     </row>
     <row r="16">
@@ -1113,41 +1113,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F16" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>18.16999999999996</v>
+        <v>0.2900000000000009</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5005843826493495</v>
+        <v>0.7142857142857117</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5591436431048979</v>
+        <v>0.2323480056796168</v>
       </c>
       <c r="K16" t="n">
         <v>0.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.251460956623374</v>
+        <v>1.785714285714279</v>
       </c>
     </row>
     <row r="17">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AMBP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1176,22 +1176,22 @@
         <v>0.04</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.989999999999981</v>
+        <v>0.2799999999999998</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4536075120139982</v>
+        <v>0.7898237445959411</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6234095735542566</v>
+        <v>0.373899882051576</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.25</v>
       </c>
       <c r="L17" t="n">
-        <v>1.058417528032663</v>
+        <v>1.777103425340867</v>
       </c>
     </row>
     <row r="18">
@@ -1201,41 +1201,41 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AMX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>VTI</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="F18" t="n">
         <v>0.05</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4899999999999984</v>
+        <v>0.75</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6853226727584039</v>
+        <v>0.8644994048821242</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2681348539558925</v>
+        <v>0.2839605887273278</v>
       </c>
       <c r="K18" t="n">
         <v>0.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.027984009137606</v>
+        <v>1.728998809764248</v>
       </c>
     </row>
     <row r="19">
@@ -1245,41 +1245,41 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2800000000000002</v>
+        <v>1.929999999999993</v>
       </c>
       <c r="I19" t="n">
-        <v>1.716738197424905</v>
+        <v>0.9383691042803455</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06869704602703308</v>
+        <v>-0.5122742960086302</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9809932556713739</v>
+        <v>1.407553656420518</v>
       </c>
     </row>
     <row r="20">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1305,25 +1305,25 @@
         <v>0.005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4199999999999999</v>
+        <v>18.16999999999996</v>
       </c>
       <c r="I20" t="n">
-        <v>1.878522229179702</v>
+        <v>0.5005843826493495</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1394286392358168</v>
+        <v>0.5591436431048979</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9392611145898505</v>
+        <v>1.251460956623374</v>
       </c>
     </row>
     <row r="21">
@@ -1333,41 +1333,41 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AMG</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.090000000000032</v>
+        <v>3.989999999999981</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4333349843953282</v>
+        <v>0.4536075120139982</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1048429141118301</v>
+        <v>0.6234095735542566</v>
       </c>
       <c r="K21" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4333349843953282</v>
+        <v>1.058417528032663</v>
       </c>
     </row>
   </sheetData>

--- a/Top20Instances_12-25-2025.xlsx
+++ b/Top20Instances_12-25-2025.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ANRO</t>
+          <t>BFLY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -563,19 +563,19 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.619999999999999</v>
+        <v>0.5400000000000005</v>
       </c>
       <c r="I3" t="n">
-        <v>6.191479952830193</v>
+        <v>8.394160583941602</v>
       </c>
       <c r="J3" t="n">
-        <v>0.59560983074749</v>
+        <v>0.4476810123559938</v>
       </c>
       <c r="K3" t="n">
         <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>9.287219929245289</v>
+        <v>12.5912408759124</v>
       </c>
     </row>
     <row r="4">
@@ -585,41 +585,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VTV</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>40.75000000000003</v>
+        <v>4.239999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>3.496730259957848</v>
+        <v>4.419595314164004</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1586042823156331</v>
+        <v>0.970275681503141</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>8.74182564989462</v>
+        <v>11.04898828541001</v>
       </c>
     </row>
     <row r="5">
@@ -629,41 +629,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AMTD</t>
+          <t>BVN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0.045</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1085999999999999</v>
+        <v>4.760000000000002</v>
       </c>
       <c r="I5" t="n">
-        <v>3.441212617779588</v>
+        <v>3.128430953005445</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.223625140291818</v>
+        <v>0.005951668645681751</v>
       </c>
       <c r="K5" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>5.161818926669382</v>
+        <v>9.385292859016335</v>
       </c>
     </row>
     <row r="6">
@@ -673,41 +673,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>ANRO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.939999999999998</v>
+        <v>1.619999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2.043681747269899</v>
+        <v>6.191479952830193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2555271636484724</v>
+        <v>0.497955154403884</v>
       </c>
       <c r="K6" t="n">
         <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>3.065522620904849</v>
+        <v>9.287219929245289</v>
       </c>
     </row>
     <row r="7">
@@ -717,41 +717,41 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AOMR</t>
+          <t>CNF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0.025</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4600000000000009</v>
+        <v>0.9714999999999998</v>
       </c>
       <c r="I7" t="n">
-        <v>1.198699821225424</v>
+        <v>2.953116066323624</v>
       </c>
       <c r="J7" t="n">
-        <v>1.013212284495868</v>
+        <v>0.2253125972856873</v>
       </c>
       <c r="K7" t="n">
         <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>2.99674955306356</v>
+        <v>8.859348198970872</v>
       </c>
     </row>
     <row r="8">
@@ -761,41 +761,41 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMRZ</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>VTV</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
         <v>0.03</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.479999999999997</v>
+        <v>40.75000000000003</v>
       </c>
       <c r="I8" t="n">
-        <v>1.849084796413902</v>
+        <v>3.496730259957848</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4952793685188084</v>
+        <v>-0.1586042823156331</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="L8" t="n">
-        <v>2.773627194620853</v>
+        <v>8.74182564989462</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -824,22 +824,22 @@
         <v>0.04</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>16.86999999999995</v>
+        <v>5.490000000000009</v>
       </c>
       <c r="I9" t="n">
-        <v>1.816071946620257</v>
+        <v>3.294117647058825</v>
       </c>
       <c r="J9" t="n">
-        <v>1.173423335033941</v>
+        <v>0.836315387398967</v>
       </c>
       <c r="K9" t="n">
         <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>2.724107919930386</v>
+        <v>8.235294117647063</v>
       </c>
     </row>
     <row r="10">
@@ -849,11 +849,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANVS</t>
+          <t>BHVN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -862,28 +862,28 @@
         </is>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.015</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.04</v>
-      </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2700000000000005</v>
+        <v>2.489999999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>5.442176870748305</v>
+        <v>4.096796043770057</v>
       </c>
       <c r="J10" t="n">
-        <v>0.69020744356314</v>
+        <v>0.7936269391476958</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="L10" t="n">
-        <v>2.721088435374151</v>
+        <v>8.193592087540116</v>
       </c>
     </row>
     <row r="11">
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>ASIX</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -906,28 +906,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>12.91999999999996</v>
+        <v>2.229999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.024485196188918</v>
+        <v>1.797409331994315</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4796649101472594</v>
+        <v>0.5595289873615017</v>
       </c>
       <c r="K11" t="n">
         <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>2.561212990472295</v>
+        <v>8.088341993974417</v>
       </c>
     </row>
     <row r="12">
@@ -937,41 +937,41 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMTB</t>
+          <t>BIRK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F12" t="n">
-        <v>0.015</v>
+        <v>0.035</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6099999999999994</v>
+        <v>5.330000000000005</v>
       </c>
       <c r="I12" t="n">
-        <v>1.608080424194935</v>
+        <v>2.906476593481078</v>
       </c>
       <c r="J12" t="n">
-        <v>0.09523330198610291</v>
+        <v>0.2685131770770344</v>
       </c>
       <c r="K12" t="n">
         <v>0.5</v>
       </c>
       <c r="L12" t="n">
-        <v>2.412120636292403</v>
+        <v>7.266191483702695</v>
       </c>
     </row>
     <row r="13">
@@ -981,41 +981,41 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AOD</t>
+          <t>BBU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4100000000000019</v>
+        <v>4.975000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8319840241796217</v>
+        <v>2.066582761285962</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4148789037526579</v>
+        <v>0.6234095735542566</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="L13" t="n">
-        <v>2.079960060449054</v>
+        <v>6.974716819340123</v>
       </c>
     </row>
     <row r="14">
@@ -1025,41 +1025,41 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AMPY</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2000000000000002</v>
+        <v>32.24999999999997</v>
       </c>
       <c r="I14" t="n">
-        <v>1.902306318012015</v>
+        <v>1.841007411629758</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7111381309541365</v>
+        <v>-0.02863205915384359</v>
       </c>
       <c r="K14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.902306318012015</v>
+        <v>6.443525940704153</v>
       </c>
     </row>
     <row r="15">
@@ -1069,41 +1069,41 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>AX</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F15" t="n">
         <v>0.03</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H15" t="n">
-        <v>14.17999999999998</v>
+        <v>8.880000000000024</v>
       </c>
       <c r="I15" t="n">
-        <v>1.821860784013596</v>
+        <v>1.823601885387882</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.09645220272003208</v>
+        <v>0.373899882051576</v>
       </c>
       <c r="K15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.821860784013596</v>
+        <v>6.382606598857587</v>
       </c>
     </row>
     <row r="16">
@@ -1113,41 +1113,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>CATO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F16" t="n">
-        <v>0.035</v>
+        <v>0.05</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2900000000000009</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7142857142857117</v>
+        <v>4.123946229209386</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2323480056796168</v>
+        <v>0.2400003701524767</v>
       </c>
       <c r="K16" t="n">
         <v>0.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.785714285714279</v>
+        <v>6.185919343814079</v>
       </c>
     </row>
     <row r="17">
@@ -1157,41 +1157,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AMBP</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2799999999999998</v>
+        <v>3.779999999999994</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7898237445959411</v>
+        <v>3.004975124378095</v>
       </c>
       <c r="J17" t="n">
-        <v>0.373899882051576</v>
+        <v>0.5127607504952669</v>
       </c>
       <c r="K17" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.777103425340867</v>
+        <v>6.00995024875619</v>
       </c>
     </row>
     <row r="18">
@@ -1201,41 +1201,41 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AMX</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H18" t="n">
-        <v>0.75</v>
+        <v>8.569999999999993</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8644994048821242</v>
+        <v>1.486486486486482</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2839605887273278</v>
+        <v>0.4796649101472594</v>
       </c>
       <c r="K18" t="n">
         <v>0.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.728998809764248</v>
+        <v>5.945945945945928</v>
       </c>
     </row>
     <row r="19">
@@ -1245,41 +1245,41 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.015</v>
+        <v>0.04</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>1.929999999999993</v>
+        <v>2.119999999999997</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9383691042803455</v>
+        <v>1.608967970888364</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5122742960086302</v>
+        <v>-0.895996170386415</v>
       </c>
       <c r="K19" t="n">
         <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.407553656420518</v>
+        <v>5.631387898109274</v>
       </c>
     </row>
     <row r="20">
@@ -1289,41 +1289,41 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>ARL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VTI</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="G20" t="n">
         <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>18.16999999999996</v>
+        <v>2.340000000000003</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5005843826493495</v>
+        <v>3.669724770642202</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5591436431048979</v>
+        <v>0.4664420834413097</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.251460956623374</v>
+        <v>5.504587155963304</v>
       </c>
     </row>
     <row r="21">
@@ -1333,11 +1333,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1346,28 +1346,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>3.989999999999981</v>
+        <v>0.7799999999999994</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4536075120139982</v>
+        <v>1.805416248746239</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6234095735542566</v>
+        <v>0.2681348539558925</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.058417528032663</v>
+        <v>5.416248746238717</v>
       </c>
     </row>
   </sheetData>
